--- a/research/traditional_assets/database/data/malawi/malawi_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/malawi/malawi_insurance_life.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.198</v>
+        <v>0.195</v>
       </c>
       <c r="E2">
-        <v>0.316</v>
+        <v>0.305</v>
       </c>
       <c r="G2">
-        <v>0.1542056074766355</v>
+        <v>0.1751792114695341</v>
       </c>
       <c r="H2">
-        <v>0.1542056074766355</v>
+        <v>0.1751792114695341</v>
       </c>
       <c r="I2">
-        <v>0.144392523364486</v>
+        <v>0.1438172043010753</v>
       </c>
       <c r="J2">
-        <v>0.1013280865715691</v>
+        <v>0.1051079632732859</v>
       </c>
       <c r="K2">
-        <v>12.9</v>
+        <v>11.8</v>
       </c>
       <c r="L2">
-        <v>0.0602803738317757</v>
+        <v>0.05286738351254481</v>
       </c>
       <c r="M2">
-        <v>5.96</v>
+        <v>6.04</v>
       </c>
       <c r="N2">
-        <v>0.08490028490028489</v>
+        <v>0.0988543371522095</v>
       </c>
       <c r="O2">
-        <v>0.462015503875969</v>
+        <v>0.5118644067796609</v>
       </c>
       <c r="P2">
-        <v>5.96</v>
+        <v>6.04</v>
       </c>
       <c r="Q2">
-        <v>0.08490028490028489</v>
+        <v>0.0988543371522095</v>
       </c>
       <c r="R2">
-        <v>0.462015503875969</v>
+        <v>0.5118644067796609</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,70 +639,61 @@
         <v>87.59999999999999</v>
       </c>
       <c r="V2">
-        <v>1.247863247863248</v>
+        <v>1.433715220949263</v>
       </c>
       <c r="W2">
-        <v>0.2993039443155452</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="X2">
-        <v>0.2175482796138414</v>
+        <v>0.2904454951763026</v>
       </c>
       <c r="Y2">
-        <v>0.08175566470170387</v>
-      </c>
-      <c r="Z2">
-        <v>32.92307692307688</v>
-      </c>
-      <c r="AA2">
-        <v>3.336032388663964</v>
+        <v>-0.06822327295408034</v>
       </c>
       <c r="AB2">
-        <v>0.1510965988983634</v>
-      </c>
-      <c r="AC2">
-        <v>3.184935789765601</v>
+        <v>0.2607999463523915</v>
       </c>
       <c r="AD2">
-        <v>57.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>57.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG2">
-        <v>-30.09999999999999</v>
+        <v>-72.09999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.4502740798747064</v>
+        <v>0.2023498694516971</v>
       </c>
       <c r="AI2">
-        <v>0.3820598006644518</v>
+        <v>0.1422018348623853</v>
       </c>
       <c r="AJ2">
-        <v>-0.7506234413965084</v>
+        <v>6.554545454545458</v>
       </c>
       <c r="AK2">
-        <v>-0.4785373608903019</v>
+        <v>-3.369158878504672</v>
       </c>
       <c r="AL2">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AM2">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AN2">
-        <v>1.742424242424242</v>
+        <v>0.4293628808864266</v>
       </c>
       <c r="AO2">
-        <v>21.16438356164383</v>
+        <v>24.31818181818182</v>
       </c>
       <c r="AP2">
-        <v>-0.912121212121212</v>
+        <v>-1.997229916897507</v>
       </c>
       <c r="AQ2">
-        <v>21.16438356164383</v>
+        <v>24.31818181818182</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +713,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.198</v>
+        <v>0.195</v>
       </c>
       <c r="E3">
-        <v>0.316</v>
+        <v>0.305</v>
       </c>
       <c r="G3">
-        <v>0.1542056074766355</v>
+        <v>0.1751792114695341</v>
       </c>
       <c r="H3">
-        <v>0.1542056074766355</v>
+        <v>0.1751792114695341</v>
       </c>
       <c r="I3">
-        <v>0.144392523364486</v>
+        <v>0.1438172043010753</v>
       </c>
       <c r="J3">
-        <v>0.1013280865715691</v>
+        <v>0.1051079632732859</v>
       </c>
       <c r="K3">
-        <v>12.9</v>
+        <v>11.8</v>
       </c>
       <c r="L3">
-        <v>0.0602803738317757</v>
+        <v>0.05286738351254481</v>
       </c>
       <c r="M3">
-        <v>5.96</v>
+        <v>6.04</v>
       </c>
       <c r="N3">
-        <v>0.08490028490028489</v>
+        <v>0.0988543371522095</v>
       </c>
       <c r="O3">
-        <v>0.462015503875969</v>
+        <v>0.5118644067796609</v>
       </c>
       <c r="P3">
-        <v>5.96</v>
+        <v>6.04</v>
       </c>
       <c r="Q3">
-        <v>0.08490028490028489</v>
+        <v>0.0988543371522095</v>
       </c>
       <c r="R3">
-        <v>0.462015503875969</v>
+        <v>0.5118644067796609</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -773,70 +764,61 @@
         <v>87.59999999999999</v>
       </c>
       <c r="V3">
-        <v>1.247863247863248</v>
+        <v>1.433715220949263</v>
       </c>
       <c r="W3">
-        <v>0.2993039443155452</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="X3">
-        <v>0.2175482796138414</v>
+        <v>0.2904454951763026</v>
       </c>
       <c r="Y3">
-        <v>0.08175566470170387</v>
-      </c>
-      <c r="Z3">
-        <v>32.92307692307688</v>
-      </c>
-      <c r="AA3">
-        <v>3.336032388663964</v>
+        <v>-0.06822327295408034</v>
       </c>
       <c r="AB3">
-        <v>0.1510965988983634</v>
-      </c>
-      <c r="AC3">
-        <v>3.184935789765601</v>
+        <v>0.2607999463523915</v>
       </c>
       <c r="AD3">
-        <v>57.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>57.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG3">
-        <v>-30.09999999999999</v>
+        <v>-72.09999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.4502740798747064</v>
+        <v>0.2023498694516971</v>
       </c>
       <c r="AI3">
-        <v>0.3820598006644518</v>
+        <v>0.1422018348623853</v>
       </c>
       <c r="AJ3">
-        <v>-0.7506234413965084</v>
+        <v>6.554545454545458</v>
       </c>
       <c r="AK3">
-        <v>-0.4785373608903019</v>
+        <v>-3.369158878504672</v>
       </c>
       <c r="AL3">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AM3">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AN3">
-        <v>1.742424242424242</v>
+        <v>0.4293628808864266</v>
       </c>
       <c r="AO3">
-        <v>21.16438356164383</v>
+        <v>24.31818181818182</v>
       </c>
       <c r="AP3">
-        <v>-0.912121212121212</v>
+        <v>-1.997229916897507</v>
       </c>
       <c r="AQ3">
-        <v>21.16438356164383</v>
+        <v>24.31818181818182</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/malawi/malawi_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/malawi/malawi_insurance_life.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.195</v>
+        <v>0.187</v>
       </c>
       <c r="E2">
-        <v>0.305</v>
+        <v>0.279</v>
       </c>
       <c r="G2">
-        <v>0.1751792114695341</v>
+        <v>0.1974837971788029</v>
       </c>
       <c r="H2">
-        <v>0.1751792114695341</v>
+        <v>0.1974837971788029</v>
       </c>
       <c r="I2">
-        <v>0.1438172043010753</v>
+        <v>0.1883339687380861</v>
       </c>
       <c r="J2">
-        <v>0.1051079632732859</v>
+        <v>0.1426067911432422</v>
       </c>
       <c r="K2">
-        <v>11.8</v>
+        <v>19.5</v>
       </c>
       <c r="L2">
-        <v>0.05286738351254481</v>
+        <v>0.07434235608082349</v>
       </c>
       <c r="M2">
-        <v>6.04</v>
+        <v>4.65</v>
       </c>
       <c r="N2">
-        <v>0.0988543371522095</v>
+        <v>0.04989270386266095</v>
       </c>
       <c r="O2">
-        <v>0.5118644067796609</v>
+        <v>0.2384615384615385</v>
       </c>
       <c r="P2">
-        <v>6.04</v>
+        <v>4.65</v>
       </c>
       <c r="Q2">
-        <v>0.0988543371522095</v>
+        <v>0.04989270386266095</v>
       </c>
       <c r="R2">
-        <v>0.5118644067796609</v>
+        <v>0.2384615384615385</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,64 +636,64 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>87.59999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="V2">
-        <v>1.433715220949263</v>
+        <v>0.8819742489270387</v>
       </c>
       <c r="W2">
-        <v>0.2222222222222222</v>
+        <v>0.3299492385786802</v>
       </c>
       <c r="X2">
-        <v>0.2904454951763026</v>
+        <v>0.2491704048089108</v>
       </c>
       <c r="Y2">
-        <v>-0.06822327295408034</v>
+        <v>0.08077883376976938</v>
       </c>
       <c r="AB2">
-        <v>0.2607999463523915</v>
+        <v>0.2204229006930994</v>
       </c>
       <c r="AD2">
-        <v>15.5</v>
+        <v>29.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>15.5</v>
+        <v>29.3</v>
       </c>
       <c r="AG2">
-        <v>-72.09999999999999</v>
+        <v>-52.90000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.2023498694516971</v>
+        <v>0.2391836734693878</v>
       </c>
       <c r="AI2">
-        <v>0.1422018348623853</v>
+        <v>0.2051820728291316</v>
       </c>
       <c r="AJ2">
-        <v>6.554545454545458</v>
+        <v>-1.312655086848636</v>
       </c>
       <c r="AK2">
-        <v>-3.369158878504672</v>
+        <v>-0.8729372937293731</v>
       </c>
       <c r="AL2">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AM2">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AN2">
-        <v>0.4293628808864266</v>
+        <v>0.5656370656370657</v>
       </c>
       <c r="AO2">
-        <v>24.31818181818182</v>
+        <v>35.79710144927537</v>
       </c>
       <c r="AP2">
-        <v>-1.997229916897507</v>
+        <v>-1.021235521235521</v>
       </c>
       <c r="AQ2">
-        <v>24.31818181818182</v>
+        <v>35.79710144927537</v>
       </c>
     </row>
     <row r="3">
@@ -713,46 +713,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.195</v>
+        <v>0.187</v>
       </c>
       <c r="E3">
-        <v>0.305</v>
+        <v>0.279</v>
       </c>
       <c r="G3">
-        <v>0.1751792114695341</v>
+        <v>0.1974837971788029</v>
       </c>
       <c r="H3">
-        <v>0.1751792114695341</v>
+        <v>0.1974837971788029</v>
       </c>
       <c r="I3">
-        <v>0.1438172043010753</v>
+        <v>0.1883339687380861</v>
       </c>
       <c r="J3">
-        <v>0.1051079632732859</v>
+        <v>0.1426067911432422</v>
       </c>
       <c r="K3">
-        <v>11.8</v>
+        <v>19.5</v>
       </c>
       <c r="L3">
-        <v>0.05286738351254481</v>
+        <v>0.07434235608082349</v>
       </c>
       <c r="M3">
-        <v>6.04</v>
+        <v>4.65</v>
       </c>
       <c r="N3">
-        <v>0.0988543371522095</v>
+        <v>0.04989270386266095</v>
       </c>
       <c r="O3">
-        <v>0.5118644067796609</v>
+        <v>0.2384615384615385</v>
       </c>
       <c r="P3">
-        <v>6.04</v>
+        <v>4.65</v>
       </c>
       <c r="Q3">
-        <v>0.0988543371522095</v>
+        <v>0.04989270386266095</v>
       </c>
       <c r="R3">
-        <v>0.5118644067796609</v>
+        <v>0.2384615384615385</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -761,64 +761,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>87.59999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="V3">
-        <v>1.433715220949263</v>
+        <v>0.8819742489270387</v>
       </c>
       <c r="W3">
-        <v>0.2222222222222222</v>
+        <v>0.3299492385786802</v>
       </c>
       <c r="X3">
-        <v>0.2904454951763026</v>
+        <v>0.2491704048089108</v>
       </c>
       <c r="Y3">
-        <v>-0.06822327295408034</v>
+        <v>0.08077883376976938</v>
       </c>
       <c r="AB3">
-        <v>0.2607999463523915</v>
+        <v>0.2204229006930994</v>
       </c>
       <c r="AD3">
-        <v>15.5</v>
+        <v>29.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>15.5</v>
+        <v>29.3</v>
       </c>
       <c r="AG3">
-        <v>-72.09999999999999</v>
+        <v>-52.90000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.2023498694516971</v>
+        <v>0.2391836734693878</v>
       </c>
       <c r="AI3">
-        <v>0.1422018348623853</v>
+        <v>0.2051820728291316</v>
       </c>
       <c r="AJ3">
-        <v>6.554545454545458</v>
+        <v>-1.312655086848636</v>
       </c>
       <c r="AK3">
-        <v>-3.369158878504672</v>
+        <v>-0.8729372937293731</v>
       </c>
       <c r="AL3">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AM3">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AN3">
-        <v>0.4293628808864266</v>
+        <v>0.5656370656370657</v>
       </c>
       <c r="AO3">
-        <v>24.31818181818182</v>
+        <v>35.79710144927537</v>
       </c>
       <c r="AP3">
-        <v>-1.997229916897507</v>
+        <v>-1.021235521235521</v>
       </c>
       <c r="AQ3">
-        <v>24.31818181818182</v>
+        <v>35.79710144927537</v>
       </c>
     </row>
   </sheetData>
